--- a/data/predictions/2026-04-15_HV.xlsx
+++ b/data/predictions/2026-04-15_HV.xlsx
@@ -539,12 +539,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -556,8 +560,10 @@
           <t>MACANESE MASTER</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -574,47 +580,79 @@
           <t>2/2/1/3/1/11</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>7.857142857142857</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6.1088</v>
-      </c>
-      <c r="R2" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>7.857142857142857</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>6.1088</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -626,8 +664,10 @@
           <t>LUCKY GENERATIONS</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -644,47 +684,79 @@
           <t>10/1/7/11/1/4</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>8.714285714285715</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.8024</v>
-      </c>
-      <c r="R3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.5</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>8.714285714285715</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.8024</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -696,8 +768,10 @@
           <t>COUNTRY DANCER</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>5</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -714,47 +788,79 @@
           <t>10/7/12/5/6/8</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.0225</v>
-      </c>
-      <c r="R4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>9.9</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.0225</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -766,8 +872,10 @@
           <t>ORIENTAL SURPRISE</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>11</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -784,47 +892,79 @@
           <t>9/5/2/9/6/4</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.428571428571429</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.0006</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4.428571428571429</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.0006</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -836,8 +976,10 @@
           <t>DOUBLE BINGO</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>6</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -854,47 +996,79 @@
           <t>4/8/5/1/3/2</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5.9486</v>
-      </c>
-      <c r="R6" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.6</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5.9486</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -906,8 +1080,10 @@
           <t>COURIER MAGIC</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>12</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -924,47 +1100,79 @@
           <t>7/5/8/3/2/2</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.8492</v>
-      </c>
-      <c r="R7" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.1</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5.8492</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -976,8 +1184,10 @@
           <t>FAMILY FORTUNE</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>8</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -994,47 +1204,79 @@
           <t>5/7/5/9/1/6</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.2472</v>
-      </c>
-      <c r="R8" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>9.300000000000001</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5.2472</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1046,8 +1288,10 @@
           <t>FLOOF</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1064,47 +1308,79 @@
           <t>11/9/14/11/7/4</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.1625</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10.2</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.1625</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1116,8 +1392,10 @@
           <t>FANTASTIC FUN</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>3</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1134,47 +1412,79 @@
           <t>2/5/5/8/7/5</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.4187</v>
-      </c>
-      <c r="R10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>6</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.14</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5.4187</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1186,8 +1496,10 @@
           <t>TAKE ACTION</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>2</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1204,47 +1516,79 @@
           <t>2/8/2/2/5/11</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.3725</v>
-      </c>
-      <c r="R11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6.3</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5.3725</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1256,8 +1600,10 @@
           <t>RUN RUN TIMING</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>6</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1274,47 +1620,79 @@
           <t>2/1/3/4/11/3</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="K12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.3627</v>
-      </c>
-      <c r="R12" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6.4</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5.3627</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1326,8 +1704,10 @@
           <t>STATE SECURITY</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>10</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1344,47 +1724,79 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.187</v>
-      </c>
-      <c r="R13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>7.6</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5.187</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1396,8 +1808,10 @@
           <t>OCEAN IMPACT</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>7</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1414,47 +1828,79 @@
           <t>11/10/4/6/1/3</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5.6189</v>
-      </c>
-      <c r="R14" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5.4</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5.6189</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1466,8 +1912,10 @@
           <t>ENTHRALLED</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>9</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1484,47 +1932,79 @@
           <t>6/3/4/7/5/4</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>10</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.5517</v>
-      </c>
-      <c r="R15" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.8</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5.5517</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1536,8 +2016,10 @@
           <t>CAN'T GO WONG</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>2</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1554,47 +2036,79 @@
           <t>5/11/4/9/4/2</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.3781</v>
-      </c>
-      <c r="R16" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6.9</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5.3781</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1606,8 +2120,10 @@
           <t>ROMANTIC FANTASY</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>6</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1624,47 +2140,79 @@
           <t>2/2/2/2/8/4</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.3494</v>
-      </c>
-      <c r="R17" t="n">
-        <v>12</v>
-      </c>
-      <c r="S17" t="n">
-        <v>7.1</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6.48</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.3494</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1676,8 +2224,10 @@
           <t>DO YOUR PART</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>5</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1694,47 +2244,79 @@
           <t>2/3/3/3/1/3</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6.086956521739131</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.3317</v>
-      </c>
-      <c r="R18" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.7</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8.52</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6.086956521739131</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6.3317</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1746,8 +2328,10 @@
           <t>WROTE A NEW PAGE</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1764,47 +2348,79 @@
           <t>11/9/3/6/2/4</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>7.652173913043478</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.8522</v>
-      </c>
-      <c r="R19" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5.9</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>8.75</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>7.652173913043478</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5.8522</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1816,8 +2432,10 @@
           <t>KING LOTUS</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>4</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1834,47 +2452,79 @@
           <t>7/11/11/4/2/2</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5.695652173913044</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.6997</v>
-      </c>
-      <c r="R20" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>6.9</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>5.695652173913044</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5.6997</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1886,8 +2536,10 @@
           <t>CALIFORNIA MOXIE</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>8</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1904,47 +2556,79 @@
           <t>6/1/7/3/1/6</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.130434782608695</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.5799</v>
-      </c>
-      <c r="R21" t="n">
-        <v>11</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7.7</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4.130434782608695</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5.5799</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1956,8 +2640,10 @@
           <t>NORTHERN FIRE BALL</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>5</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1974,47 +2660,79 @@
           <t>12/4/1/4/8/6</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>10</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.5433</v>
-      </c>
-      <c r="R22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>6.8</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>5.5433</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2026,8 +2744,10 @@
           <t>CLOUD NINE</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>9</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2044,47 +2764,79 @@
           <t>4/7/3</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.4985</v>
-      </c>
-      <c r="R23" t="n">
-        <v>12</v>
-      </c>
-      <c r="S23" t="n">
-        <v>7.1</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5.4985</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2096,8 +2848,10 @@
           <t>STORMING DRAGON</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>11</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2114,47 +2868,79 @@
           <t>3/3/6/5/5/5</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>10</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.4887</v>
-      </c>
-      <c r="R24" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="S24" t="n">
-        <v>7.1</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5.4887</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2166,8 +2952,10 @@
           <t>PRESTIGE HALL</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>10</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2184,47 +2972,79 @@
           <t>2/2/2/6/4/7</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.3606</v>
-      </c>
-      <c r="R25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>8.199999999999999</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5.3606</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2236,8 +3056,10 @@
           <t>MASTER LUCKY</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>2</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2254,47 +3076,79 @@
           <t>7/2/4/1</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>9</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.433</v>
-      </c>
-      <c r="R26" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6.433</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>24.7</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2306,8 +3160,10 @@
           <t>GENIUS BABY</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>5</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2324,47 +3180,79 @@
           <t>3/2/9/4/4/1</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="K27" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.9675</v>
-      </c>
-      <c r="R27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S27" t="n">
-        <v>5.5</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6.95</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>5.9675</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2376,8 +3264,10 @@
           <t>ARGENTO OCEAN</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>8</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2394,47 +3284,79 @@
           <t>5/2/5/1/4/7</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>10</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5.782</v>
-      </c>
-      <c r="R28" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S28" t="n">
-        <v>6.6</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5.782</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2446,8 +3368,10 @@
           <t>THE HEIR</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>4</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2464,47 +3388,79 @@
           <t>2/3/3/8/4/6</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K29" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>7</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.4992</v>
-      </c>
-      <c r="R29" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S29" t="n">
-        <v>8.800000000000001</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5.4992</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2516,8 +3472,10 @@
           <t>RIDING TOGETHER</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>9</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2534,47 +3492,79 @@
           <t>11/1/6/6/4/1</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>9.470588235294118</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>5.887</v>
-      </c>
-      <c r="R30" t="n">
-        <v>18</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4.7</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>6.62</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>9.470588235294118</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>5.887</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2586,8 +3576,10 @@
           <t>KEEFY</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>6</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2604,47 +3596,79 @@
           <t>2/3/4/5/9/7</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="K31" t="n">
-        <v>7</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>10</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.3774</v>
-      </c>
-      <c r="R31" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>7.9</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>5.3774</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2656,8 +3680,10 @@
           <t>FIVEFORTWO</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>8</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2674,47 +3700,79 @@
           <t>1/4/10/6/1/12</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="K32" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>8.941176470588236</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.3215</v>
-      </c>
-      <c r="R32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>8.300000000000001</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>8.941176470588236</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5.3215</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2726,8 +3784,10 @@
           <t>ALL ROUND WINNER</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>7</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2744,47 +3804,79 @@
           <t>3/6/6/3/1/6</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="K33" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.2899</v>
-      </c>
-      <c r="R33" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S33" t="n">
-        <v>8.6</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>6.38</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5.2899</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2796,8 +3888,10 @@
           <t>LUCKY PLANET</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>2</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2814,47 +3908,79 @@
           <t>12/6/1/2/1/3</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="K34" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>8.941176470588236</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.5241</v>
-      </c>
-      <c r="R34" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.8</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>8.24</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>8.941176470588236</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>6.5241</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2866,8 +3992,10 @@
           <t>AMAZING KID</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>12</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2884,47 +4012,79 @@
           <t>3/1/7/1/1/1</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>5.235294117647059</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.1345</v>
-      </c>
-      <c r="R35" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5.6</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>5.235294117647059</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6.1345</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2936,8 +4096,10 @@
           <t>SYMBOL OF STRENGTH</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>3</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2954,47 +4116,79 @@
           <t>5/1/3/4/6/5</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="K36" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>10</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5.9003</v>
-      </c>
-      <c r="R36" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="S36" t="n">
-        <v>7.1</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>8.05</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>5.9003</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3006,8 +4200,10 @@
           <t>STRAIGHT TO GLORY</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>7</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3024,39 +4220,67 @@
           <t>2/6/1/1/2/5</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="K37" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.588235294117647</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5.7735</v>
-      </c>
-      <c r="R37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8.1</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>7.71</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2.588235294117647</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>5.7735</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3235,7 +4459,6 @@
           <t>11/1/6/6/4/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.62</v>
       </c>
@@ -3316,7 +4539,6 @@
           <t>2/3/4/5/9/7</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>4.33</v>
       </c>
@@ -3397,7 +4619,6 @@
           <t>1/4/10/6/1/12</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.62</v>
       </c>
@@ -3478,7 +4699,6 @@
           <t>3/6/6/3/1/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.38</v>
       </c>
@@ -3559,7 +4779,6 @@
           <t>7/3/1/8/2/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.43</v>
       </c>
@@ -3640,7 +4859,6 @@
           <t>14/7/3/6/4/11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.95</v>
       </c>
@@ -3721,7 +4939,6 @@
           <t>11/13/11/8/6/4</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.33</v>
       </c>
@@ -3802,7 +5019,6 @@
           <t>8/5/8/5/5/10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.29</v>
       </c>
@@ -3883,7 +5099,6 @@
           <t>6/9/4</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.33</v>
       </c>
@@ -3964,7 +5179,6 @@
           <t>1/7/10/4/9/6</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.67</v>
       </c>
@@ -4045,7 +5259,6 @@
           <t>10/4/10/7/6/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.57</v>
       </c>
@@ -4257,7 +5470,6 @@
           <t>12/6/1/2/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.24</v>
       </c>
@@ -4338,7 +5550,6 @@
           <t>3/1/7/1/1/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>8.9</v>
       </c>
@@ -4419,7 +5630,6 @@
           <t>5/1/3/4/6/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.86</v>
       </c>
@@ -4500,7 +5710,6 @@
           <t>2/6/1/1/2/5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>7.71</v>
       </c>
@@ -4581,7 +5790,6 @@
           <t>9/2/5/1/7/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.57</v>
       </c>
@@ -4662,7 +5870,6 @@
           <t>6/2/4/10/2/1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>7.1</v>
       </c>
@@ -4743,7 +5950,6 @@
           <t>9/7/12/9/11/1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4</v>
       </c>
@@ -4824,7 +6030,6 @@
           <t>1/1/10/7/11/1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5.24</v>
       </c>
@@ -4905,7 +6110,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>5</v>
       </c>
@@ -4986,7 +6190,6 @@
           <t>6/5/11/13</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.1</v>
       </c>
@@ -5067,7 +6270,6 @@
           <t>10/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -5337,7 +6539,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>5</t>
@@ -5439,7 +6640,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>7</t>
@@ -5541,7 +6741,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
@@ -5643,7 +6842,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>5</t>
@@ -5745,7 +6943,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>4</t>
@@ -5847,7 +7044,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>2</t>
@@ -5949,7 +7145,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>3</t>
@@ -6051,7 +7246,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>4</t>
@@ -6153,7 +7347,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>2</t>
@@ -6428,7 +7621,6 @@
           <t>2/2/1/3/1/11</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.9</v>
       </c>
@@ -6509,7 +7701,6 @@
           <t>10/1/7/11/1/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.71</v>
       </c>
@@ -6590,7 +7781,6 @@
           <t>10/7/12/5/6/8</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>2.95</v>
       </c>
@@ -6671,7 +7861,6 @@
           <t>9/5/2/9/6/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.9</v>
       </c>
@@ -6752,7 +7941,6 @@
           <t>12/4/8/10/4/6</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.67</v>
       </c>
@@ -6833,7 +8021,6 @@
           <t>7/5/4/9/11/8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2.67</v>
       </c>
@@ -6914,7 +8101,6 @@
           <t>8/11/2/4/12/9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.43</v>
       </c>
@@ -6995,7 +8181,6 @@
           <t>14/5/12/8/12/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1.57</v>
       </c>
@@ -7076,7 +8261,6 @@
           <t>12/10/10/11/11/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1</v>
       </c>
@@ -7242,7 +8426,6 @@
           <t>11/10/10/12/10/13</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1</v>
       </c>
@@ -7539,7 +8722,6 @@
           <t>4/8/5/1/3/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.57</v>
       </c>
@@ -7620,7 +8802,6 @@
           <t>7/5/8/3/2/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.14</v>
       </c>
@@ -7701,7 +8882,6 @@
           <t>5/7/5/9/1/6</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.14</v>
       </c>
@@ -7782,7 +8962,6 @@
           <t>11/9/14/11/7/4</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>3</v>
       </c>
@@ -7863,7 +9042,6 @@
           <t>4/8/3/5/5/2</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>6.33</v>
       </c>
@@ -7944,7 +9122,6 @@
           <t>14/7/13/5/12/4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.38</v>
       </c>
@@ -8025,7 +9202,6 @@
           <t>11/7/11/6/8/5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.14</v>
       </c>
@@ -8106,7 +9282,6 @@
           <t>7/6/9/8/10/4</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.14</v>
       </c>
@@ -8187,7 +9362,6 @@
           <t>3/6/3/8/7/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.14</v>
       </c>
@@ -8268,7 +9442,6 @@
           <t>9/4/10/7/4/5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>4.24</v>
       </c>
@@ -8349,7 +9522,6 @@
           <t>11/10/4/7/9/12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.33</v>
       </c>
@@ -8430,7 +9602,6 @@
           <t>8/13/9/10/9/9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.71</v>
       </c>
@@ -8642,7 +9813,6 @@
           <t>2/5/5/8/7/5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>4.14</v>
       </c>
@@ -8723,7 +9893,6 @@
           <t>2/8/2/2/5/11</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.1</v>
       </c>
@@ -8804,7 +9973,6 @@
           <t>2/1/3/4/11/3</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.19</v>
       </c>
@@ -8885,7 +10053,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -8966,7 +10133,6 @@
           <t>10/8/8/6/5/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.33</v>
       </c>
@@ -9047,7 +10213,6 @@
           <t>6/7/5/9/7/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.71</v>
       </c>
@@ -9128,7 +10293,6 @@
           <t>4/10/5/12/10/3</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.81</v>
       </c>
@@ -9209,7 +10373,6 @@
           <t>11/9/3/8/12/8</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.57</v>
       </c>
@@ -9290,7 +10453,6 @@
           <t>7/5/4/6/7/8</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.52</v>
       </c>
@@ -9371,7 +10533,6 @@
           <t>12/13/5/11/13/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.86</v>
       </c>
@@ -9452,7 +10613,6 @@
           <t>4/7/8/10/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.8</v>
       </c>
@@ -9533,7 +10693,6 @@
           <t>5/12/12/6/14/10</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.76</v>
       </c>
@@ -9745,7 +10904,6 @@
           <t>11/10/4/6/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.43</v>
       </c>
@@ -9826,7 +10984,6 @@
           <t>6/3/4/7/5/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.29</v>
       </c>
@@ -9907,7 +11064,6 @@
           <t>5/11/4/9/4/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.57</v>
       </c>
@@ -10073,7 +11229,6 @@
           <t>9/9/2/6/5/10</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.81</v>
       </c>
@@ -10154,7 +11309,6 @@
           <t>12/5/13/11/4/4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4</v>
       </c>
@@ -10235,7 +11389,6 @@
           <t>3/5/7/10/9/9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.52</v>
       </c>
@@ -10316,7 +11469,6 @@
           <t>3/4/3/4/10/8</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.05</v>
       </c>
@@ -10397,7 +11549,6 @@
           <t>3/9/8/10/11/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.57</v>
       </c>
@@ -10478,7 +11629,6 @@
           <t>2/6/7/7/12/8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.62</v>
       </c>
@@ -10559,7 +11709,6 @@
           <t>7/12/7/10/4/11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.57</v>
       </c>
@@ -10856,7 +12005,6 @@
           <t>2/3/3/3/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.52</v>
       </c>
@@ -10937,7 +12085,6 @@
           <t>11/9/3/6/2/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6</v>
       </c>
@@ -11018,7 +12165,6 @@
           <t>7/11/11/4/2/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.24</v>
       </c>
@@ -11099,7 +12245,6 @@
           <t>6/1/7/3/1/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.62</v>
       </c>
@@ -11180,7 +12325,6 @@
           <t>3/2/7/5/5/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.38</v>
       </c>
@@ -11261,7 +12405,6 @@
           <t>10/11/4/1/7/3</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.9</v>
       </c>
@@ -11427,7 +12570,6 @@
           <t>4/14/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.33</v>
       </c>
@@ -11593,7 +12735,6 @@
           <t>10/10/5/9/9/8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.29</v>
       </c>
@@ -11674,7 +12815,6 @@
           <t>8/11/10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.17</v>
       </c>
@@ -11886,7 +13026,6 @@
           <t>12/4/1/4/8/6</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>4.81</v>
       </c>
@@ -11967,7 +13106,6 @@
           <t>4/7/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6</v>
       </c>
@@ -12048,7 +13186,6 @@
           <t>3/3/6/5/5/5</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5.29</v>
       </c>
@@ -12129,7 +13266,6 @@
           <t>2/2/2/6/4/7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.62</v>
       </c>
@@ -12210,7 +13346,6 @@
           <t>1/4/9/1/11/8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.05</v>
       </c>
@@ -12291,7 +13426,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -12372,7 +13506,6 @@
           <t>1/11/7/11/10/3</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.71</v>
       </c>
@@ -12453,7 +13586,6 @@
           <t>6/3/8/13/8/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.05</v>
       </c>
@@ -12534,7 +13666,6 @@
           <t>4/5/10/6/8/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.43</v>
       </c>
@@ -12615,7 +13746,6 @@
           <t>12/8/6/12/11/7</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.1</v>
       </c>
@@ -12696,7 +13826,6 @@
           <t>7/11/12/12/11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>1.13</v>
       </c>
@@ -12777,7 +13906,6 @@
           <t>12/14/12/12/11/11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
       </c>
@@ -12989,7 +14117,6 @@
           <t>7/2/4/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.9</v>
       </c>
@@ -13070,7 +14197,6 @@
           <t>3/2/9/4/4/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.95</v>
       </c>
@@ -13151,7 +14277,6 @@
           <t>5/2/5/1/4/7</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6</v>
       </c>
@@ -13232,7 +14357,6 @@
           <t>2/3/3/8/4/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.29</v>
       </c>
@@ -13313,7 +14437,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -13394,7 +14517,6 @@
           <t>8/6/6/6/4/9</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.81</v>
       </c>
@@ -13475,7 +14597,6 @@
           <t>2/1/11/6/7/11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.29</v>
       </c>
@@ -13556,7 +14677,6 @@
           <t>14/14/10/2/6/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.1</v>
       </c>
@@ -13637,7 +14757,6 @@
           <t>11/1/9/8/9/12</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.43</v>
       </c>
@@ -13718,7 +14837,6 @@
           <t>1/4/4/14/10/8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.9</v>
       </c>
@@ -13799,7 +14917,6 @@
           <t>11/7/5/8/9/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.76</v>
       </c>
@@ -13880,7 +14997,6 @@
           <t>12/14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1</v>
       </c>
